--- a/owp/owp-2108-live/cortex output files/2108_Test_Labels_Match_Score.xlsx
+++ b/owp/owp-2108-live/cortex output files/2108_Test_Labels_Match_Score.xlsx
@@ -405,48 +405,52 @@
     <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
   </cellStyleXfs>
-  <cellXfs count="11">
+  <cellXfs count="12">
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="164" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="6" fillId="2" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="164" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="164" fontId="6" fillId="2" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="164" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="7" fillId="3" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="164" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="7" fillId="3" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="7" fillId="4" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="164" fontId="7" fillId="4" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="9" fillId="5" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="164" fontId="9" fillId="5" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -705,238 +709,238 @@
   <dimension ref="A1:F20"/>
   <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" customHeight="false" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="24"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="10"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="0" width="30"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="0" width="16"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="0" width="10"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="0" width="60"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="24"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="1" width="10"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="1" width="30"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="1" width="16"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="1" width="10"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="1" width="60"/>
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="17.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A1" s="1" t="s">
+      <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A2" s="2" t="s">
+      <c r="A2" s="3" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A4" s="3" t="s">
+      <c r="A4" s="4" t="s">
         <v>2</v>
       </c>
-      <c r="B4" s="3" t="s">
+      <c r="B4" s="4" t="s">
         <v>3</v>
       </c>
-      <c r="C4" s="3" t="s">
+      <c r="C4" s="4" t="s">
         <v>4</v>
       </c>
-      <c r="D4" s="3" t="s">
+      <c r="D4" s="4" t="s">
         <v>5</v>
       </c>
-      <c r="E4" s="3" t="s">
+      <c r="E4" s="4" t="s">
         <v>6</v>
       </c>
-      <c r="F4" s="3" t="s">
+      <c r="F4" s="4" t="s">
         <v>7</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A5" s="4" t="s">
+      <c r="A5" s="5" t="s">
         <v>8</v>
       </c>
-      <c r="B5" s="5" t="n">
+      <c r="B5" s="6" t="n">
         <v>21</v>
       </c>
-      <c r="C5" s="5" t="s">
+      <c r="C5" s="6" t="s">
         <v>9</v>
       </c>
-      <c r="D5" s="5" t="s">
+      <c r="D5" s="6" t="s">
         <v>10</v>
       </c>
-      <c r="E5" s="6" t="s">
+      <c r="E5" s="7" t="s">
         <v>11</v>
       </c>
-      <c r="F5" s="7" t="s">
+      <c r="F5" s="8" t="s">
         <v>12</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A6" s="4" t="s">
+      <c r="A6" s="5" t="s">
         <v>13</v>
       </c>
-      <c r="B6" s="5" t="n">
+      <c r="B6" s="6" t="n">
         <v>52</v>
       </c>
-      <c r="C6" s="5" t="s">
+      <c r="C6" s="6" t="s">
         <v>14</v>
       </c>
-      <c r="D6" s="5" t="s">
+      <c r="D6" s="6" t="s">
         <v>15</v>
       </c>
-      <c r="E6" s="8" t="s">
+      <c r="E6" s="9" t="s">
         <v>16</v>
       </c>
-      <c r="F6" s="7" t="s">
+      <c r="F6" s="8" t="s">
         <v>17</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="32.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A7" s="4" t="s">
+      <c r="A7" s="5" t="s">
         <v>18</v>
       </c>
-      <c r="B7" s="5" t="n">
+      <c r="B7" s="6" t="n">
         <v>7</v>
       </c>
-      <c r="C7" s="5" t="s">
+      <c r="C7" s="6" t="s">
         <v>19</v>
       </c>
-      <c r="D7" s="5" t="s">
+      <c r="D7" s="6" t="s">
         <v>20</v>
       </c>
-      <c r="E7" s="8" t="s">
+      <c r="E7" s="9" t="s">
         <v>16</v>
       </c>
-      <c r="F7" s="7" t="s">
+      <c r="F7" s="8" t="s">
         <v>21</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="22.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A8" s="4" t="s">
+      <c r="A8" s="5" t="s">
         <v>22</v>
       </c>
-      <c r="B8" s="5" t="n">
+      <c r="B8" s="6" t="n">
         <v>2</v>
       </c>
-      <c r="C8" s="5" t="s">
+      <c r="C8" s="6" t="s">
         <v>23</v>
       </c>
-      <c r="D8" s="5" t="s">
+      <c r="D8" s="6" t="s">
         <v>24</v>
       </c>
-      <c r="E8" s="8" t="s">
+      <c r="E8" s="9" t="s">
         <v>16</v>
       </c>
-      <c r="F8" s="7" t="s">
+      <c r="F8" s="8" t="s">
         <v>25</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A9" s="4" t="s">
+      <c r="A9" s="5" t="s">
         <v>26</v>
       </c>
-      <c r="B9" s="5" t="n">
+      <c r="B9" s="6" t="n">
         <v>36</v>
       </c>
-      <c r="C9" s="5" t="s">
+      <c r="C9" s="6" t="s">
         <v>27</v>
       </c>
-      <c r="D9" s="5" t="s">
+      <c r="D9" s="6" t="s">
         <v>28</v>
       </c>
-      <c r="E9" s="8" t="s">
+      <c r="E9" s="9" t="s">
         <v>16</v>
       </c>
-      <c r="F9" s="7" t="s">
+      <c r="F9" s="8" t="s">
         <v>29</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="22.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A10" s="4" t="s">
+      <c r="A10" s="5" t="s">
         <v>30</v>
       </c>
-      <c r="B10" s="5" t="n">
+      <c r="B10" s="6" t="n">
         <v>7</v>
       </c>
-      <c r="C10" s="5" t="s">
+      <c r="C10" s="6" t="s">
         <v>31</v>
       </c>
-      <c r="D10" s="5" t="s">
+      <c r="D10" s="6" t="s">
         <v>32</v>
       </c>
-      <c r="E10" s="8" t="s">
+      <c r="E10" s="9" t="s">
         <v>16</v>
       </c>
-      <c r="F10" s="7" t="s">
+      <c r="F10" s="8" t="s">
         <v>33</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="22.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A11" s="4" t="s">
+      <c r="A11" s="5" t="s">
         <v>34</v>
       </c>
-      <c r="B11" s="5" t="n">
+      <c r="B11" s="6" t="n">
         <v>1</v>
       </c>
-      <c r="C11" s="5" t="s">
+      <c r="C11" s="6" t="s">
         <v>35</v>
       </c>
-      <c r="D11" s="5" t="s">
+      <c r="D11" s="6" t="s">
         <v>36</v>
       </c>
-      <c r="E11" s="8" t="s">
+      <c r="E11" s="9" t="s">
         <v>16</v>
       </c>
-      <c r="F11" s="7" t="s">
+      <c r="F11" s="8" t="s">
         <v>37</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A14" s="9" t="s">
+      <c r="A14" s="10" t="s">
         <v>38</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="79.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A15" s="10" t="s">
+      <c r="A15" s="11" t="s">
         <v>39</v>
       </c>
-      <c r="B15" s="10"/>
-      <c r="C15" s="10"/>
-      <c r="D15" s="10"/>
-      <c r="E15" s="10"/>
-      <c r="F15" s="10"/>
+      <c r="B15" s="11"/>
+      <c r="C15" s="11"/>
+      <c r="D15" s="11"/>
+      <c r="E15" s="11"/>
+      <c r="F15" s="11"/>
     </row>
     <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A16" s="10"/>
-      <c r="B16" s="10"/>
-      <c r="C16" s="10"/>
-      <c r="D16" s="10"/>
-      <c r="E16" s="10"/>
-      <c r="F16" s="10"/>
+      <c r="A16" s="11"/>
+      <c r="B16" s="11"/>
+      <c r="C16" s="11"/>
+      <c r="D16" s="11"/>
+      <c r="E16" s="11"/>
+      <c r="F16" s="11"/>
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A17" s="10"/>
-      <c r="B17" s="10"/>
-      <c r="C17" s="10"/>
-      <c r="D17" s="10"/>
-      <c r="E17" s="10"/>
-      <c r="F17" s="10"/>
+      <c r="A17" s="11"/>
+      <c r="B17" s="11"/>
+      <c r="C17" s="11"/>
+      <c r="D17" s="11"/>
+      <c r="E17" s="11"/>
+      <c r="F17" s="11"/>
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A18" s="10"/>
-      <c r="B18" s="10"/>
-      <c r="C18" s="10"/>
-      <c r="D18" s="10"/>
-      <c r="E18" s="10"/>
-      <c r="F18" s="10"/>
+      <c r="A18" s="11"/>
+      <c r="B18" s="11"/>
+      <c r="C18" s="11"/>
+      <c r="D18" s="11"/>
+      <c r="E18" s="11"/>
+      <c r="F18" s="11"/>
     </row>
     <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A19" s="10"/>
-      <c r="B19" s="10"/>
-      <c r="C19" s="10"/>
-      <c r="D19" s="10"/>
-      <c r="E19" s="10"/>
-      <c r="F19" s="10"/>
+      <c r="A19" s="11"/>
+      <c r="B19" s="11"/>
+      <c r="C19" s="11"/>
+      <c r="D19" s="11"/>
+      <c r="E19" s="11"/>
+      <c r="F19" s="11"/>
     </row>
     <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A20" s="10"/>
-      <c r="B20" s="10"/>
-      <c r="C20" s="10"/>
-      <c r="D20" s="10"/>
-      <c r="E20" s="10"/>
-      <c r="F20" s="10"/>
+      <c r="A20" s="11"/>
+      <c r="B20" s="11"/>
+      <c r="C20" s="11"/>
+      <c r="D20" s="11"/>
+      <c r="E20" s="11"/>
+      <c r="F20" s="11"/>
     </row>
   </sheetData>
   <mergeCells count="1">
@@ -960,341 +964,341 @@
   <dimension ref="A1:M10"/>
   <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" customHeight="false" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="12"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="28"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="13" min="3" style="0" width="12"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="12"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="1" width="28"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="13" min="3" style="1" width="12"/>
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="17.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A1" s="1" t="s">
+      <c r="A1" s="2" t="s">
         <v>40</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A3" s="3" t="s">
+      <c r="A3" s="4" t="s">
         <v>41</v>
       </c>
-      <c r="B3" s="3" t="s">
+      <c r="B3" s="4" t="s">
         <v>42</v>
       </c>
-      <c r="C3" s="3" t="s">
+      <c r="C3" s="4" t="s">
         <v>43</v>
       </c>
-      <c r="D3" s="3" t="s">
+      <c r="D3" s="4" t="s">
         <v>44</v>
       </c>
-      <c r="E3" s="3" t="s">
+      <c r="E3" s="4" t="s">
         <v>45</v>
       </c>
-      <c r="F3" s="3" t="s">
+      <c r="F3" s="4" t="s">
         <v>46</v>
       </c>
-      <c r="G3" s="3" t="s">
+      <c r="G3" s="4" t="s">
         <v>47</v>
       </c>
-      <c r="H3" s="3" t="s">
+      <c r="H3" s="4" t="s">
         <v>48</v>
       </c>
-      <c r="I3" s="3" t="s">
+      <c r="I3" s="4" t="s">
         <v>49</v>
       </c>
-      <c r="J3" s="3" t="s">
+      <c r="J3" s="4" t="s">
         <v>50</v>
       </c>
-      <c r="K3" s="3" t="s">
+      <c r="K3" s="4" t="s">
         <v>51</v>
       </c>
-      <c r="L3" s="3" t="s">
+      <c r="L3" s="4" t="s">
         <v>52</v>
       </c>
-      <c r="M3" s="3" t="s">
+      <c r="M3" s="4" t="s">
         <v>53</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A4" s="0" t="s">
+      <c r="A4" s="1" t="s">
         <v>54</v>
       </c>
-      <c r="B4" s="0" t="s">
+      <c r="B4" s="1" t="s">
         <v>55</v>
       </c>
-      <c r="C4" s="0" t="n">
-        <v>0</v>
-      </c>
-      <c r="D4" s="0" t="n">
-        <v>0</v>
-      </c>
-      <c r="E4" s="0" t="n">
+      <c r="C4" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="D4" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="E4" s="1" t="n">
         <v>2134.5</v>
       </c>
-      <c r="F4" s="0" t="n">
+      <c r="F4" s="1" t="n">
         <v>2134.5</v>
       </c>
-      <c r="G4" s="0" t="n">
-        <v>0</v>
-      </c>
-      <c r="H4" s="0" t="n">
-        <v>0</v>
-      </c>
-      <c r="I4" s="0" t="n">
+      <c r="G4" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="H4" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="I4" s="1" t="n">
         <v>32.5</v>
       </c>
-      <c r="J4" s="0" t="n">
-        <v>0</v>
-      </c>
-      <c r="K4" s="0" t="n">
-        <v>0</v>
-      </c>
-      <c r="L4" s="0" t="n">
-        <v>0</v>
-      </c>
-      <c r="M4" s="8" t="s">
+      <c r="J4" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="K4" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="L4" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="M4" s="9" t="s">
         <v>56</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A5" s="0" t="s">
+      <c r="A5" s="1" t="s">
         <v>57</v>
       </c>
-      <c r="B5" s="0" t="s">
+      <c r="B5" s="1" t="s">
         <v>58</v>
       </c>
-      <c r="C5" s="0" t="n">
-        <v>0</v>
-      </c>
-      <c r="D5" s="0" t="n">
-        <v>0</v>
-      </c>
-      <c r="E5" s="0" t="n">
+      <c r="C5" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="D5" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="E5" s="1" t="n">
         <v>106487.5</v>
       </c>
-      <c r="F5" s="0" t="n">
+      <c r="F5" s="1" t="n">
         <v>106487.5</v>
       </c>
-      <c r="G5" s="0" t="n">
-        <v>0</v>
-      </c>
-      <c r="H5" s="0" t="n">
-        <v>0</v>
-      </c>
-      <c r="I5" s="0" t="n">
-        <v>0</v>
-      </c>
-      <c r="J5" s="0" t="n">
-        <v>0</v>
-      </c>
-      <c r="K5" s="0" t="n">
-        <v>0</v>
-      </c>
-      <c r="L5" s="0" t="n">
-        <v>0</v>
-      </c>
-      <c r="M5" s="8" t="s">
+      <c r="G5" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="H5" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="I5" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="J5" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="K5" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="L5" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="M5" s="9" t="s">
         <v>56</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A6" s="0" t="s">
+      <c r="A6" s="1" t="s">
         <v>59</v>
       </c>
-      <c r="B6" s="0" t="s">
+      <c r="B6" s="1" t="s">
         <v>60</v>
       </c>
-      <c r="C6" s="0" t="n">
-        <v>0</v>
-      </c>
-      <c r="D6" s="0" t="n">
-        <v>0</v>
-      </c>
-      <c r="E6" s="0" t="n">
+      <c r="C6" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="D6" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="E6" s="1" t="n">
         <v>922.35</v>
       </c>
-      <c r="F6" s="0" t="n">
+      <c r="F6" s="1" t="n">
         <v>922.35</v>
       </c>
-      <c r="G6" s="0" t="n">
-        <v>0</v>
-      </c>
-      <c r="H6" s="0" t="n">
-        <v>0</v>
-      </c>
-      <c r="I6" s="0" t="n">
-        <v>0</v>
-      </c>
-      <c r="J6" s="0" t="n">
-        <v>0</v>
-      </c>
-      <c r="K6" s="0" t="n">
-        <v>0</v>
-      </c>
-      <c r="L6" s="0" t="n">
-        <v>0</v>
-      </c>
-      <c r="M6" s="8" t="s">
+      <c r="G6" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="H6" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="I6" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="J6" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="K6" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="L6" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="M6" s="9" t="s">
         <v>56</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A7" s="0" t="s">
+      <c r="A7" s="1" t="s">
         <v>61</v>
       </c>
-      <c r="B7" s="0" t="s">
+      <c r="B7" s="1" t="s">
         <v>62</v>
       </c>
-      <c r="C7" s="0" t="n">
-        <v>0</v>
-      </c>
-      <c r="D7" s="0" t="n">
-        <v>0</v>
-      </c>
-      <c r="E7" s="0" t="n">
+      <c r="C7" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="D7" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="E7" s="1" t="n">
         <v>6402</v>
       </c>
-      <c r="F7" s="0" t="n">
+      <c r="F7" s="1" t="n">
         <v>6402</v>
       </c>
-      <c r="G7" s="0" t="n">
-        <v>0</v>
-      </c>
-      <c r="H7" s="0" t="n">
-        <v>0</v>
-      </c>
-      <c r="I7" s="0" t="n">
-        <v>0</v>
-      </c>
-      <c r="J7" s="0" t="n">
-        <v>0</v>
-      </c>
-      <c r="K7" s="0" t="n">
-        <v>0</v>
-      </c>
-      <c r="L7" s="0" t="n">
-        <v>0</v>
-      </c>
-      <c r="M7" s="8" t="s">
+      <c r="G7" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="H7" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="I7" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="J7" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="K7" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="L7" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="M7" s="9" t="s">
         <v>56</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A8" s="0" t="s">
+      <c r="A8" s="1" t="s">
         <v>63</v>
       </c>
-      <c r="B8" s="0" t="s">
+      <c r="B8" s="1" t="s">
         <v>64</v>
       </c>
-      <c r="C8" s="0" t="n">
-        <v>0</v>
-      </c>
-      <c r="D8" s="0" t="n">
-        <v>0</v>
-      </c>
-      <c r="E8" s="0" t="n">
+      <c r="C8" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="D8" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="E8" s="1" t="n">
         <v>1052.32</v>
       </c>
-      <c r="F8" s="0" t="n">
+      <c r="F8" s="1" t="n">
         <v>1052.32</v>
       </c>
-      <c r="G8" s="0" t="n">
-        <v>0</v>
-      </c>
-      <c r="H8" s="0" t="n">
-        <v>0</v>
-      </c>
-      <c r="I8" s="0" t="n">
-        <v>0</v>
-      </c>
-      <c r="J8" s="0" t="n">
-        <v>0</v>
-      </c>
-      <c r="K8" s="0" t="n">
-        <v>0</v>
-      </c>
-      <c r="L8" s="0" t="n">
-        <v>0</v>
-      </c>
-      <c r="M8" s="8" t="s">
+      <c r="G8" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="H8" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="I8" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="J8" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="K8" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="L8" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="M8" s="9" t="s">
         <v>56</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A9" s="0" t="s">
+      <c r="A9" s="1" t="s">
         <v>65</v>
       </c>
-      <c r="B9" s="0" t="s">
+      <c r="B9" s="1" t="s">
         <v>66</v>
       </c>
-      <c r="C9" s="0" t="n">
-        <v>0</v>
-      </c>
-      <c r="D9" s="0" t="n">
-        <v>0</v>
-      </c>
-      <c r="E9" s="0" t="n">
+      <c r="C9" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="D9" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="E9" s="1" t="n">
         <v>163.3</v>
       </c>
-      <c r="F9" s="0" t="n">
+      <c r="F9" s="1" t="n">
         <v>163.3</v>
       </c>
-      <c r="G9" s="0" t="n">
-        <v>0</v>
-      </c>
-      <c r="H9" s="0" t="n">
-        <v>0</v>
-      </c>
-      <c r="I9" s="0" t="n">
-        <v>0</v>
-      </c>
-      <c r="J9" s="0" t="n">
-        <v>0</v>
-      </c>
-      <c r="K9" s="0" t="n">
-        <v>0</v>
-      </c>
-      <c r="L9" s="0" t="n">
-        <v>0</v>
-      </c>
-      <c r="M9" s="8" t="s">
+      <c r="G9" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="H9" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="I9" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="J9" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="K9" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="L9" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="M9" s="9" t="s">
         <v>56</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A10" s="0" t="s">
+      <c r="A10" s="1" t="s">
         <v>67</v>
       </c>
-      <c r="B10" s="0" t="s">
+      <c r="B10" s="1" t="s">
         <v>68</v>
       </c>
-      <c r="C10" s="0" t="n">
-        <v>0</v>
-      </c>
-      <c r="D10" s="0" t="n">
-        <v>0</v>
-      </c>
-      <c r="E10" s="0" t="n">
+      <c r="C10" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="D10" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="E10" s="1" t="n">
         <v>91402</v>
       </c>
-      <c r="F10" s="0" t="n">
+      <c r="F10" s="1" t="n">
         <v>-91402</v>
       </c>
-      <c r="G10" s="0" t="n">
-        <v>0</v>
-      </c>
-      <c r="H10" s="0" t="n">
-        <v>0</v>
-      </c>
-      <c r="I10" s="0" t="n">
-        <v>0</v>
-      </c>
-      <c r="J10" s="0" t="n">
-        <v>0</v>
-      </c>
-      <c r="K10" s="0" t="n">
-        <v>0</v>
-      </c>
-      <c r="L10" s="0" t="n">
-        <v>0</v>
-      </c>
-      <c r="M10" s="8" t="s">
+      <c r="G10" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="H10" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="I10" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="J10" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="K10" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="L10" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="M10" s="9" t="s">
         <v>56</v>
       </c>
     </row>
@@ -1317,108 +1321,108 @@
   <dimension ref="A1:J5"/>
   <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" customHeight="false" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="28"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="10" min="2" style="0" width="12"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="28"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="10" min="2" style="1" width="12"/>
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="17.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A1" s="1" t="s">
+      <c r="A1" s="2" t="s">
         <v>69</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A3" s="3" t="s">
+      <c r="A3" s="4" t="s">
         <v>70</v>
       </c>
-      <c r="B3" s="3" t="s">
+      <c r="B3" s="4" t="s">
         <v>71</v>
       </c>
-      <c r="C3" s="3" t="s">
+      <c r="C3" s="4" t="s">
         <v>49</v>
       </c>
-      <c r="D3" s="3" t="s">
+      <c r="D3" s="4" t="s">
         <v>50</v>
       </c>
-      <c r="E3" s="3" t="s">
+      <c r="E3" s="4" t="s">
         <v>51</v>
       </c>
-      <c r="F3" s="3" t="s">
+      <c r="F3" s="4" t="s">
         <v>52</v>
       </c>
-      <c r="G3" s="3" t="s">
+      <c r="G3" s="4" t="s">
         <v>72</v>
       </c>
-      <c r="H3" s="3" t="s">
+      <c r="H3" s="4" t="s">
         <v>73</v>
       </c>
-      <c r="I3" s="3" t="s">
+      <c r="I3" s="4" t="s">
         <v>74</v>
       </c>
-      <c r="J3" s="3" t="s">
+      <c r="J3" s="4" t="s">
         <v>53</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A4" s="0" t="s">
+      <c r="A4" s="1" t="s">
         <v>75</v>
       </c>
-      <c r="B4" s="0" t="s">
+      <c r="B4" s="1" t="s">
         <v>76</v>
       </c>
-      <c r="C4" s="0" t="n">
+      <c r="C4" s="1" t="n">
         <v>12</v>
       </c>
-      <c r="D4" s="0" t="n">
-        <v>0</v>
-      </c>
-      <c r="E4" s="0" t="n">
-        <v>0</v>
-      </c>
-      <c r="F4" s="0" t="n">
-        <v>0</v>
-      </c>
-      <c r="G4" s="0" t="n">
+      <c r="D4" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="E4" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="F4" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="G4" s="1" t="n">
         <v>720</v>
       </c>
-      <c r="H4" s="0" t="n">
-        <v>0</v>
-      </c>
-      <c r="I4" s="0" t="n">
+      <c r="H4" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="I4" s="1" t="n">
         <v>60</v>
       </c>
-      <c r="J4" s="8" t="s">
+      <c r="J4" s="9" t="s">
         <v>77</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A5" s="0" t="s">
+      <c r="A5" s="1" t="s">
         <v>78</v>
       </c>
-      <c r="B5" s="0" t="s">
+      <c r="B5" s="1" t="s">
         <v>76</v>
       </c>
-      <c r="C5" s="0" t="n">
+      <c r="C5" s="1" t="n">
         <v>20.5</v>
       </c>
-      <c r="D5" s="0" t="n">
-        <v>0</v>
-      </c>
-      <c r="E5" s="0" t="n">
-        <v>0</v>
-      </c>
-      <c r="F5" s="0" t="n">
-        <v>0</v>
-      </c>
-      <c r="G5" s="0" t="n">
+      <c r="D5" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="E5" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="F5" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="G5" s="1" t="n">
         <v>1414.5</v>
       </c>
-      <c r="H5" s="0" t="n">
-        <v>0</v>
-      </c>
-      <c r="I5" s="0" t="n">
+      <c r="H5" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="I5" s="1" t="n">
         <v>69</v>
       </c>
-      <c r="J5" s="8" t="s">
+      <c r="J5" s="9" t="s">
         <v>77</v>
       </c>
     </row>
